--- a/docs/REVISION-CAMPO.xlsx
+++ b/docs/REVISION-CAMPO.xlsx
@@ -72,21 +72,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4E4"/>
+        <bgColor rgb="FFFCE4E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>

--- a/docs/REVISION-CAMPO.xlsx
+++ b/docs/REVISION-CAMPO.xlsx
@@ -121,38 +121,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/docs/REVISION-CAMPO.xlsx
+++ b/docs/REVISION-CAMPO.xlsx
@@ -537,7 +537,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Última ficha en el sistema: 2026-08-05  ·  Generado: 12/08/2026</t>
+          <t>Última ficha en el sistema: 2026-08-05  ·  Generado: 13/08/2026</t>
         </is>
       </c>
     </row>

--- a/docs/REVISION-CAMPO.xlsx
+++ b/docs/REVISION-CAMPO.xlsx
@@ -578,7 +578,7 @@
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Desde el 9 de agosto de 2026 este archivo aplica las reglas de «no aplica» que acordó la coordinación del proyecto. Con el criterio anterior salían 9.161 datos faltantes; el trabajo real de campo son 775.</t>
+          <t>Desde el 9 de agosto de 2026 este archivo aplica las reglas de «no aplica» que acordó la coordinación del proyecto. Con el criterio anterior salían 9.188 datos faltantes; el trabajo real de campo son 775.</t>
         </is>
       </c>
     </row>

--- a/docs/REVISION-CAMPO.xlsx
+++ b/docs/REVISION-CAMPO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resueltos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resumen'!$A$1:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Resumen'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pendientes'!$A$1:$J$776</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fuera de campo'!$A$1:$J$259</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resueltos'!$A$1:$C$27</definedName>
@@ -769,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1041,35 +1041,35 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ASOC. PITANA BAJO</t>
+          <t>LOS ANDES IZACATA</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN ROSALÍA</t>
+          <t>ASOC. PITANA BAJO</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>LOS ANDES IZACATA</t>
+          <t>ASOCIACIÓN ROSALÍA</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
@@ -1157,7 +1157,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>MILAGRO</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -1171,42 +1171,42 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>OTONCITO</t>
+          <t>MILAGRO</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
         <v>11</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN SAN PEDRO</t>
+          <t>OTONCITO</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6" t="n">
         <v>10</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>8</v>
       </c>
       <c r="D29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>ASOCIACIÓN SAN PEDRO</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
     </row>
@@ -1269,7 +1269,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
@@ -1311,7 +1311,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>PANBAMAQUITO</t>
+          <t>PAMBAMARQUITO</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
@@ -1381,7 +1381,7 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>LOS ANDES INSACATA</t>
+          <t>PUEBLO DE ASCÁZUBI</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
@@ -1395,21 +1395,21 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>PUEBLO DE ASCÁZUBI</t>
+          <t>HDA. SAN FRANSISCO</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>COMUNA IZACATA</t>
+          <t>SR. HERNÁN TIMPE</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
@@ -1421,53 +1421,25 @@
       <c r="D45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>HDA. SAN FRANSISCO</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>SR. HERNÁN TIMPE</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>ALPAKA</t>
         </is>
       </c>
-      <c r="B48" s="10" t="n">
+      <c r="B46" s="10" t="n">
         <v>212</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C46" s="10" t="n">
         <v>192</v>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>NO CUENTAN COMO PENDIENTE — son lotes de fraccionamiento cargados en bloque, no fichas levantadas en campo (ver REPORTE-PENDIENTES.md). Están en la hoja «Fuera de campo».</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D48"/>
+  <autoFilter ref="A1:D46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15260,7 +15232,7 @@
     <row r="314">
       <c r="A314" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B314" s="12" t="inlineStr">
@@ -15304,7 +15276,7 @@
     <row r="315">
       <c r="A315" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B315" s="12" t="inlineStr">
@@ -15348,7 +15320,7 @@
     <row r="316">
       <c r="A316" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B316" s="12" t="inlineStr">
@@ -15392,7 +15364,7 @@
     <row r="317">
       <c r="A317" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B317" s="12" t="inlineStr">
@@ -15436,7 +15408,7 @@
     <row r="318">
       <c r="A318" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B318" s="12" t="inlineStr">
@@ -15480,7 +15452,7 @@
     <row r="319">
       <c r="A319" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B319" s="12" t="inlineStr">
@@ -15524,7 +15496,7 @@
     <row r="320">
       <c r="A320" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B320" s="12" t="inlineStr">
@@ -15568,7 +15540,7 @@
     <row r="321">
       <c r="A321" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B321" s="12" t="inlineStr">
@@ -15612,22 +15584,22 @@
     <row r="322">
       <c r="A322" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B322" s="12" t="inlineStr">
         <is>
-          <t>1702521580093</t>
+          <t>1702521580014</t>
         </is>
       </c>
       <c r="C322" s="12" t="inlineStr">
         <is>
-          <t>CHOLANGO SALAZAR MARIA ISABEL</t>
+          <t>AULES TUTILLO ESTEBAN</t>
         </is>
       </c>
       <c r="D322" s="12" t="inlineStr">
         <is>
-          <t>1709156986</t>
+          <t>1708978315</t>
         </is>
       </c>
       <c r="E322" s="12" t="inlineStr">
@@ -15637,7 +15609,7 @@
       </c>
       <c r="F322" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor3</t>
+          <t>u0_a70</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr">
@@ -15649,34 +15621,34 @@
       <c r="I322" s="13" t="n"/>
       <c r="J322" s="12" t="inlineStr">
         <is>
-          <t>{02809de2-588d-4642-bc9c-cd4b04fad170}</t>
+          <t>{752a487c-94a1-49ed-9704-793c66a6dc91}</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="12" t="inlineStr">
         <is>
-          <t>COMUNA INSACATA</t>
+          <t>COMUNA IZACATA</t>
         </is>
       </c>
       <c r="B323" s="12" t="inlineStr">
         <is>
-          <t>1702521580137</t>
+          <t>1702521580093</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>TIPANLUISA CHOLANGO ANA LUISA</t>
+          <t>CHOLANGO SALAZAR MARIA ISABEL</t>
         </is>
       </c>
       <c r="D323" s="12" t="inlineStr">
         <is>
-          <t>1717871543</t>
+          <t>1709156986</t>
         </is>
       </c>
       <c r="E323" s="12" t="inlineStr">
         <is>
-          <t>energía eléctrica</t>
+          <t>teléfono</t>
         </is>
       </c>
       <c r="F323" s="12" t="inlineStr">
@@ -15693,7 +15665,7 @@
       <c r="I323" s="13" t="n"/>
       <c r="J323" s="12" t="inlineStr">
         <is>
-          <t>{ce6a3917-00f2-4f32-84ab-94ab8f0afcd4}</t>
+          <t>{02809de2-588d-4642-bc9c-cd4b04fad170}</t>
         </is>
       </c>
     </row>
@@ -15705,27 +15677,27 @@
       </c>
       <c r="B324" s="12" t="inlineStr">
         <is>
-          <t>1702521580014</t>
+          <t>1702521580137</t>
         </is>
       </c>
       <c r="C324" s="12" t="inlineStr">
         <is>
-          <t>AULES TUTILLO ESTEBAN</t>
+          <t>TIPANLUISA CHOLANGO ANA LUISA</t>
         </is>
       </c>
       <c r="D324" s="12" t="inlineStr">
         <is>
-          <t>1708978315</t>
+          <t>1717871543</t>
         </is>
       </c>
       <c r="E324" s="12" t="inlineStr">
         <is>
-          <t>teléfono</t>
+          <t>energía eléctrica</t>
         </is>
       </c>
       <c r="F324" s="12" t="inlineStr">
         <is>
-          <t>u0_a70</t>
+          <t>jvk-editor3</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr">
@@ -15737,7 +15709,7 @@
       <c r="I324" s="13" t="n"/>
       <c r="J324" s="12" t="inlineStr">
         <is>
-          <t>{752a487c-94a1-49ed-9704-793c66a6dc91}</t>
+          <t>{ce6a3917-00f2-4f32-84ab-94ab8f0afcd4}</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17212,7 @@
     <row r="359">
       <c r="A359" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B359" s="12" t="inlineStr">
@@ -17284,7 +17256,7 @@
     <row r="360">
       <c r="A360" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B360" s="12" t="inlineStr">
@@ -17328,7 +17300,7 @@
     <row r="361">
       <c r="A361" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B361" s="12" t="inlineStr">
@@ -17372,7 +17344,7 @@
     <row r="362">
       <c r="A362" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B362" s="12" t="inlineStr">
@@ -17416,7 +17388,7 @@
     <row r="363">
       <c r="A363" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B363" s="12" t="inlineStr">
@@ -17460,7 +17432,7 @@
     <row r="364">
       <c r="A364" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B364" s="12" t="inlineStr">
@@ -17504,7 +17476,7 @@
     <row r="365">
       <c r="A365" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B365" s="12" t="inlineStr">
@@ -17548,7 +17520,7 @@
     <row r="366">
       <c r="A366" s="12" t="inlineStr">
         <is>
-          <t>INSACATA GRANDE</t>
+          <t>IZACATA GRANDE</t>
         </is>
       </c>
       <c r="B366" s="12" t="inlineStr">
@@ -23432,22 +23404,22 @@
     <row r="500">
       <c r="A500" s="12" t="inlineStr">
         <is>
-          <t>LOS ANDES INSACATA</t>
+          <t>LOS ANDES IZACATA</t>
         </is>
       </c>
       <c r="B500" s="12" t="inlineStr">
         <is>
-          <t>1702521580063</t>
+          <t>1702521100016</t>
         </is>
       </c>
       <c r="C500" s="12" t="inlineStr">
         <is>
-          <t>TIPANLUISA LANCHIMBA MARIA ROSA ELENA</t>
+          <t>CHOLANGO SALAZAR PEDRO LORENZO</t>
         </is>
       </c>
       <c r="D500" s="12" t="inlineStr">
         <is>
-          <t>1704573201</t>
+          <t>1713298857</t>
         </is>
       </c>
       <c r="E500" s="12" t="inlineStr">
@@ -23457,7 +23429,7 @@
       </c>
       <c r="F500" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor6</t>
+          <t>mayralisseth201</t>
         </is>
       </c>
       <c r="G500" s="13" t="inlineStr">
@@ -23469,39 +23441,39 @@
       <c r="I500" s="13" t="n"/>
       <c r="J500" s="12" t="inlineStr">
         <is>
-          <t>{ab2672b8-be3b-4fa7-9a70-6310362651f5}</t>
+          <t>{10c8267b-5301-4a5d-be67-269478c705a8}</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="12" t="inlineStr">
         <is>
-          <t>LOS ANDES INSACATA</t>
+          <t>LOS ANDES IZACATA</t>
         </is>
       </c>
       <c r="B501" s="12" t="inlineStr">
         <is>
-          <t>1702521580075</t>
+          <t>1702521100017</t>
         </is>
       </c>
       <c r="C501" s="12" t="inlineStr">
         <is>
-          <t>LANCHIMBA SALAZAR RAMON</t>
+          <t>CHOLANGO SALAZAR JOSE MARIA</t>
         </is>
       </c>
       <c r="D501" s="12" t="inlineStr">
         <is>
-          <t>1703987287</t>
+          <t>1712092418</t>
         </is>
       </c>
       <c r="E501" s="12" t="inlineStr">
         <is>
-          <t>teléfono</t>
+          <t>agua de consumo</t>
         </is>
       </c>
       <c r="F501" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor6</t>
+          <t>jvk-editor2</t>
         </is>
       </c>
       <c r="G501" s="13" t="inlineStr">
@@ -23513,7 +23485,7 @@
       <c r="I501" s="13" t="n"/>
       <c r="J501" s="12" t="inlineStr">
         <is>
-          <t>{1bd29cba-d690-4ef4-9f2f-cb3214640466}</t>
+          <t>{63d4d5e4-d0f7-43f7-b0ba-7d9b3924066c}</t>
         </is>
       </c>
     </row>
@@ -23525,27 +23497,27 @@
       </c>
       <c r="B502" s="12" t="inlineStr">
         <is>
-          <t>1702521100016</t>
+          <t>1702521100017</t>
         </is>
       </c>
       <c r="C502" s="12" t="inlineStr">
         <is>
-          <t>CHOLANGO SALAZAR PEDRO LORENZO</t>
+          <t>CHOLANGO SALAZAR JOSE MARIA</t>
         </is>
       </c>
       <c r="D502" s="12" t="inlineStr">
         <is>
-          <t>1713298857</t>
+          <t>1712092418</t>
         </is>
       </c>
       <c r="E502" s="12" t="inlineStr">
         <is>
-          <t>teléfono</t>
+          <t>energía eléctrica</t>
         </is>
       </c>
       <c r="F502" s="12" t="inlineStr">
         <is>
-          <t>mayralisseth201</t>
+          <t>jvk-editor2</t>
         </is>
       </c>
       <c r="G502" s="13" t="inlineStr">
@@ -23557,7 +23529,7 @@
       <c r="I502" s="13" t="n"/>
       <c r="J502" s="12" t="inlineStr">
         <is>
-          <t>{10c8267b-5301-4a5d-be67-269478c705a8}</t>
+          <t>{63d4d5e4-d0f7-43f7-b0ba-7d9b3924066c}</t>
         </is>
       </c>
     </row>
@@ -23569,27 +23541,27 @@
       </c>
       <c r="B503" s="12" t="inlineStr">
         <is>
-          <t>1702521100017</t>
+          <t>1702521100031</t>
         </is>
       </c>
       <c r="C503" s="12" t="inlineStr">
         <is>
-          <t>CHOLANGO SALAZAR JOSE MARIA</t>
+          <t>PILCA TIPANLUISA MIGUEL</t>
         </is>
       </c>
       <c r="D503" s="12" t="inlineStr">
         <is>
-          <t>1712092418</t>
+          <t>1708442973</t>
         </is>
       </c>
       <c r="E503" s="12" t="inlineStr">
         <is>
-          <t>agua de consumo</t>
+          <t>teléfono</t>
         </is>
       </c>
       <c r="F503" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor2</t>
+          <t>jvk-editor3</t>
         </is>
       </c>
       <c r="G503" s="13" t="inlineStr">
@@ -23601,7 +23573,7 @@
       <c r="I503" s="13" t="n"/>
       <c r="J503" s="12" t="inlineStr">
         <is>
-          <t>{63d4d5e4-d0f7-43f7-b0ba-7d9b3924066c}</t>
+          <t>{218e153b-9d30-4e99-9105-9d0b99e0b2d2}</t>
         </is>
       </c>
     </row>
@@ -23613,17 +23585,17 @@
       </c>
       <c r="B504" s="12" t="inlineStr">
         <is>
-          <t>1702521100017</t>
+          <t>1702521100051</t>
         </is>
       </c>
       <c r="C504" s="12" t="inlineStr">
         <is>
-          <t>CHOLANGO SALAZAR JOSE MARIA</t>
+          <t>TANDAYAMO AULES MARIA ROSA</t>
         </is>
       </c>
       <c r="D504" s="12" t="inlineStr">
         <is>
-          <t>1712092418</t>
+          <t>1709284077</t>
         </is>
       </c>
       <c r="E504" s="12" t="inlineStr">
@@ -23633,7 +23605,7 @@
       </c>
       <c r="F504" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor2</t>
+          <t>jvk-editor3</t>
         </is>
       </c>
       <c r="G504" s="13" t="inlineStr">
@@ -23645,7 +23617,7 @@
       <c r="I504" s="13" t="n"/>
       <c r="J504" s="12" t="inlineStr">
         <is>
-          <t>{63d4d5e4-d0f7-43f7-b0ba-7d9b3924066c}</t>
+          <t>{a739d781-5bea-40eb-820f-312622ead4bb}</t>
         </is>
       </c>
     </row>
@@ -23657,17 +23629,17 @@
       </c>
       <c r="B505" s="12" t="inlineStr">
         <is>
-          <t>1702521100031</t>
+          <t>1702521100051</t>
         </is>
       </c>
       <c r="C505" s="12" t="inlineStr">
         <is>
-          <t>PILCA TIPANLUISA MIGUEL</t>
+          <t>TANDAYAMO AULES MARIA ROSA</t>
         </is>
       </c>
       <c r="D505" s="12" t="inlineStr">
         <is>
-          <t>1708442973</t>
+          <t>1709284077</t>
         </is>
       </c>
       <c r="E505" s="12" t="inlineStr">
@@ -23689,7 +23661,7 @@
       <c r="I505" s="13" t="n"/>
       <c r="J505" s="12" t="inlineStr">
         <is>
-          <t>{218e153b-9d30-4e99-9105-9d0b99e0b2d2}</t>
+          <t>{a739d781-5bea-40eb-820f-312622ead4bb}</t>
         </is>
       </c>
     </row>
@@ -23701,27 +23673,27 @@
       </c>
       <c r="B506" s="12" t="inlineStr">
         <is>
-          <t>1702521100051</t>
+          <t>1702521100059</t>
         </is>
       </c>
       <c r="C506" s="12" t="inlineStr">
         <is>
-          <t>TANDAYAMO AULES MARIA ROSA</t>
+          <t>CHIQUIMBA AULES SEGUNDO TOMAS</t>
         </is>
       </c>
       <c r="D506" s="12" t="inlineStr">
         <is>
-          <t>1709284077</t>
+          <t>1712045408</t>
         </is>
       </c>
       <c r="E506" s="12" t="inlineStr">
         <is>
-          <t>energía eléctrica</t>
+          <t>teléfono</t>
         </is>
       </c>
       <c r="F506" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor3</t>
+          <t>jvk-editor4</t>
         </is>
       </c>
       <c r="G506" s="13" t="inlineStr">
@@ -23733,7 +23705,7 @@
       <c r="I506" s="13" t="n"/>
       <c r="J506" s="12" t="inlineStr">
         <is>
-          <t>{a739d781-5bea-40eb-820f-312622ead4bb}</t>
+          <t>{8a14a901-5b96-4b4c-b4f6-965262893aaa}</t>
         </is>
       </c>
     </row>
@@ -23745,17 +23717,17 @@
       </c>
       <c r="B507" s="12" t="inlineStr">
         <is>
-          <t>1702521100051</t>
+          <t>1702521100098</t>
         </is>
       </c>
       <c r="C507" s="12" t="inlineStr">
         <is>
-          <t>TANDAYAMO AULES MARIA ROSA</t>
+          <t>TIPANLUISA LANCHIMBA MARIA HORTENCIA</t>
         </is>
       </c>
       <c r="D507" s="12" t="inlineStr">
         <is>
-          <t>1709284077</t>
+          <t>1709058414</t>
         </is>
       </c>
       <c r="E507" s="12" t="inlineStr">
@@ -23765,7 +23737,7 @@
       </c>
       <c r="F507" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor3</t>
+          <t>mayralisseth201</t>
         </is>
       </c>
       <c r="G507" s="13" t="inlineStr">
@@ -23777,7 +23749,7 @@
       <c r="I507" s="13" t="n"/>
       <c r="J507" s="12" t="inlineStr">
         <is>
-          <t>{a739d781-5bea-40eb-820f-312622ead4bb}</t>
+          <t>{9219b46d-f60a-4de1-83fe-e5d444ea950a}</t>
         </is>
       </c>
     </row>
@@ -23789,17 +23761,17 @@
       </c>
       <c r="B508" s="12" t="inlineStr">
         <is>
-          <t>1702521100059</t>
+          <t>1702521100102</t>
         </is>
       </c>
       <c r="C508" s="12" t="inlineStr">
         <is>
-          <t>CHIQUIMBA AULES SEGUNDO TOMAS</t>
+          <t>TIPANLUISA LANCHIMBA SILVIA GLORIA</t>
         </is>
       </c>
       <c r="D508" s="12" t="inlineStr">
         <is>
-          <t>1712045408</t>
+          <t>1717872137</t>
         </is>
       </c>
       <c r="E508" s="12" t="inlineStr">
@@ -23821,7 +23793,7 @@
       <c r="I508" s="13" t="n"/>
       <c r="J508" s="12" t="inlineStr">
         <is>
-          <t>{8a14a901-5b96-4b4c-b4f6-965262893aaa}</t>
+          <t>{d59bcd00-f38b-44c4-b751-445b5c8bbe7b}</t>
         </is>
       </c>
     </row>
@@ -23833,27 +23805,27 @@
       </c>
       <c r="B509" s="12" t="inlineStr">
         <is>
-          <t>1702521100098</t>
+          <t>1702521100134</t>
         </is>
       </c>
       <c r="C509" s="12" t="inlineStr">
         <is>
-          <t>TIPANLUISA LANCHIMBA MARIA HORTENCIA</t>
+          <t>CHOLANGO TIPANLUISA MILTON RODRIGO</t>
         </is>
       </c>
       <c r="D509" s="12" t="inlineStr">
         <is>
-          <t>1709058414</t>
+          <t>1716784887</t>
         </is>
       </c>
       <c r="E509" s="12" t="inlineStr">
         <is>
-          <t>teléfono</t>
+          <t>nivel de instrucción</t>
         </is>
       </c>
       <c r="F509" s="12" t="inlineStr">
         <is>
-          <t>mayralisseth201</t>
+          <t>jvk-corp</t>
         </is>
       </c>
       <c r="G509" s="13" t="inlineStr">
@@ -23865,7 +23837,7 @@
       <c r="I509" s="13" t="n"/>
       <c r="J509" s="12" t="inlineStr">
         <is>
-          <t>{9219b46d-f60a-4de1-83fe-e5d444ea950a}</t>
+          <t>{2622e877-ed2e-4bc0-b165-19b25405ca4b}</t>
         </is>
       </c>
     </row>
@@ -23877,17 +23849,17 @@
       </c>
       <c r="B510" s="12" t="inlineStr">
         <is>
-          <t>1702521100102</t>
+          <t>1702521100134</t>
         </is>
       </c>
       <c r="C510" s="12" t="inlineStr">
         <is>
-          <t>TIPANLUISA LANCHIMBA SILVIA GLORIA</t>
+          <t>CHOLANGO TIPANLUISA MILTON RODRIGO</t>
         </is>
       </c>
       <c r="D510" s="12" t="inlineStr">
         <is>
-          <t>1717872137</t>
+          <t>1716784887</t>
         </is>
       </c>
       <c r="E510" s="12" t="inlineStr">
@@ -23897,7 +23869,7 @@
       </c>
       <c r="F510" s="12" t="inlineStr">
         <is>
-          <t>jvk-editor4</t>
+          <t>jvk-corp</t>
         </is>
       </c>
       <c r="G510" s="13" t="inlineStr">
@@ -23909,7 +23881,7 @@
       <c r="I510" s="13" t="n"/>
       <c r="J510" s="12" t="inlineStr">
         <is>
-          <t>{d59bcd00-f38b-44c4-b751-445b5c8bbe7b}</t>
+          <t>{2622e877-ed2e-4bc0-b165-19b25405ca4b}</t>
         </is>
       </c>
     </row>
@@ -23921,27 +23893,27 @@
       </c>
       <c r="B511" s="12" t="inlineStr">
         <is>
-          <t>1702521100134</t>
+          <t>1702521580063</t>
         </is>
       </c>
       <c r="C511" s="12" t="inlineStr">
         <is>
-          <t>CHOLANGO TIPANLUISA MILTON RODRIGO</t>
+          <t>TIPANLUISA LANCHIMBA MARIA ROSA ELENA</t>
         </is>
       </c>
       <c r="D511" s="12" t="inlineStr">
         <is>
-          <t>1716784887</t>
+          <t>1704573201</t>
         </is>
       </c>
       <c r="E511" s="12" t="inlineStr">
         <is>
-          <t>nivel de instrucción</t>
+          <t>teléfono</t>
         </is>
       </c>
       <c r="F511" s="12" t="inlineStr">
         <is>
-          <t>jvk-corp</t>
+          <t>jvk-editor6</t>
         </is>
       </c>
       <c r="G511" s="13" t="inlineStr">
@@ -23953,7 +23925,7 @@
       <c r="I511" s="13" t="n"/>
       <c r="J511" s="12" t="inlineStr">
         <is>
-          <t>{2622e877-ed2e-4bc0-b165-19b25405ca4b}</t>
+          <t>{ab2672b8-be3b-4fa7-9a70-6310362651f5}</t>
         </is>
       </c>
     </row>
@@ -23965,17 +23937,17 @@
       </c>
       <c r="B512" s="12" t="inlineStr">
         <is>
-          <t>1702521100134</t>
+          <t>1702521580075</t>
         </is>
       </c>
       <c r="C512" s="12" t="inlineStr">
         <is>
-          <t>CHOLANGO TIPANLUISA MILTON RODRIGO</t>
+          <t>LANCHIMBA SALAZAR RAMON</t>
         </is>
       </c>
       <c r="D512" s="12" t="inlineStr">
         <is>
-          <t>1716784887</t>
+          <t>1703987287</t>
         </is>
       </c>
       <c r="E512" s="12" t="inlineStr">
@@ -23985,7 +23957,7 @@
       </c>
       <c r="F512" s="12" t="inlineStr">
         <is>
-          <t>jvk-corp</t>
+          <t>jvk-editor6</t>
         </is>
       </c>
       <c r="G512" s="13" t="inlineStr">
@@ -23997,7 +23969,7 @@
       <c r="I512" s="13" t="n"/>
       <c r="J512" s="12" t="inlineStr">
         <is>
-          <t>{2622e877-ed2e-4bc0-b165-19b25405ca4b}</t>
+          <t>{1bd29cba-d690-4ef4-9f2f-cb3214640466}</t>
         </is>
       </c>
     </row>
@@ -26636,7 +26608,7 @@
     <row r="573">
       <c r="A573" s="12" t="inlineStr">
         <is>
-          <t>PANBAMAQUITO</t>
+          <t>PAMBAMARQUITO</t>
         </is>
       </c>
       <c r="B573" s="12" t="inlineStr">
@@ -26680,7 +26652,7 @@
     <row r="574">
       <c r="A574" s="12" t="inlineStr">
         <is>
-          <t>PANBAMAQUITO</t>
+          <t>PAMBAMARQUITO</t>
         </is>
       </c>
       <c r="B574" s="12" t="inlineStr">
@@ -26724,7 +26696,7 @@
     <row r="575">
       <c r="A575" s="12" t="inlineStr">
         <is>
-          <t>PANBAMAQUITO</t>
+          <t>PAMBAMARQUITO</t>
         </is>
       </c>
       <c r="B575" s="12" t="inlineStr">
@@ -26768,7 +26740,7 @@
     <row r="576">
       <c r="A576" s="12" t="inlineStr">
         <is>
-          <t>PANBAMAQUITO</t>
+          <t>PAMBAMARQUITO</t>
         </is>
       </c>
       <c r="B576" s="12" t="inlineStr">
@@ -26812,7 +26784,7 @@
     <row r="577">
       <c r="A577" s="12" t="inlineStr">
         <is>
-          <t>PANBAMAQUITO</t>
+          <t>PAMBAMARQUITO</t>
         </is>
       </c>
       <c r="B577" s="12" t="inlineStr">
